--- a/GUA/IPPU/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
+++ b/GUA/IPPU/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\openmodels_lac\GUA\Modelos\PIUP\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Downloads\IPPU_GUA_v1_2025\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD36414-4B94-4ECB-9BDA-0E69AC17705F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F3D6D4-377D-4E51-AE53-A04F18AEE4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Other_Params" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -536,7 +536,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -603,17 +603,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a085176836abd262a7ea2e14f8197063">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18610519e5d66159880ace7e9acb3815" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
     <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
     <xsd:element name="properties">
@@ -655,7 +646,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -708,7 +699,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -727,7 +718,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -744,8 +735,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -834,26 +825,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F471FCA4-AE43-4A31-8D17-9F0FE78EDA70}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D044BD7-CD13-4950-8112-F2F737605A34}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
     <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C332EBF3-94CE-4B27-9EE4-04F4A7C12B22}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0EE994F-6845-4372-AF2D-C9C110B7CEC2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C92A595D-2322-4A32-BC16-09D6C916ED50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -869,4 +863,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD3AFD5D-B2EB-4B7C-B9D5-F081DC0BCFEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>